--- a/jogos_2025-01-08.xlsx
+++ b/jogos_2025-01-08.xlsx
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['45', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI7" t="n">
         <v>2.05</v>
       </c>
-      <c r="M7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AJ7" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['28', '57']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45665.60416666666</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X8" t="n">
         <v>2.7</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Y8" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '57']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['45', '90+5']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45665.60416666666</v>
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['23', '83']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>4.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45665.69791666666</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,65 +1830,65 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>14</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>3.55</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['23', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45665.69791666666</v>
